--- a/reports/二级子公司C_利润表_2026-04.xlsx
+++ b/reports/二级子公司C_利润表_2026-04.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>90794500</v>
+        <v>92551084</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>88168000</v>
+        <v>87863673</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>306791680</v>
+        <v>305855839</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>412000</v>
+        <v>414018</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1549120</v>
+        <v>1553819</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>360500</v>
+        <v>361598</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1355480</v>
+        <v>1360341</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>309000</v>
+        <v>309204</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1161840</v>
+        <v>1165915</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>288400</v>
+        <v>287868</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1084384</v>
+        <v>1087434</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>154500</v>
+        <v>153878</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>580920</v>
+        <v>581862</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>123600</v>
+        <v>122921</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>464736</v>
+        <v>464804</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>89146500</v>
+        <v>90901597</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>86520000</v>
+        <v>86214186</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82400000</v>
+        <v>82075543</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>285104000</v>
+        <v>284192453</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1236000</v>
+        <v>1233856</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4647360</v>
+        <v>4630530</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>824000</v>
+        <v>824638</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3098240</v>
+        <v>3088374</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3090000</v>
+        <v>3099723</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>11618400</v>
+        <v>11592989</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>412000</v>
+        <v>414046</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1549120</v>
+        <v>1547873</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>309000</v>
+        <v>310826</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1161840</v>
+        <v>1162675</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>515000</v>
+        <v>517995</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>1936400</v>
+        <v>1940497</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>618000</v>
+        <v>620902</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2323680</v>
+        <v>2330978</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2575000</v>
+        <v>2582085</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>9682000</v>
+        <v>9716982</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>51500</v>
+        <v>51517</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>193640</v>
+        <v>206724</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1233326</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4659810</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>820483</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3102692</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>61542500</v>
+        <v>65686686</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>54796000</v>
+        <v>54507692</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>53560000</v>
+        <v>53276237</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>201385600</v>
+        <v>200830604</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1236000</v>
+        <v>1231455</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>4647360</v>
+        <v>4631167</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2057098</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>7717721</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>659930</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2470954</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>413413</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1545990</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>496944</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1857819</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>373010</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1395488</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>248615</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>931590</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>206923</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>777069</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>927000</v>
+        <v>929269</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3485520</v>
+        <v>3498168</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>721000</v>
+        <v>720989</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2710960</v>
+        <v>2720123</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>618000</v>
+        <v>616471</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2323680</v>
+        <v>2329575</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4635000</v>
+        <v>4614149</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>17427600</v>
+        <v>17449335</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>206000</v>
+        <v>204819</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>774560</v>
+        <v>774357</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>360500</v>
+        <v>358353</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1355480</v>
+        <v>1439855</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>412000</v>
+        <v>358353</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1549120</v>
+        <v>1439855</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>51500</v>
+        <v>51325</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>193640</v>
+        <v>205288</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>185200</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>738932</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>361018</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1351457</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>124057</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>493381</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>93192</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>370555</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>155425</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>618532</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>517890</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1941113</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>82750</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>330656</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>61932</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>248094</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>102964</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>413398</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>71900</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>289142</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51257</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>206266</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40960</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>164767</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30718</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>123394</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27604000</v>
+        <v>26485493</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32290500</v>
+        <v>29866353</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>205847</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>771833</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51591</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>205384</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>82400</v>
+        <v>82726</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>309824</v>
+        <v>328976</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27521600</v>
+        <v>26608614</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2884000</v>
+        <v>2901304</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>10843840</v>
+        <v>11548185</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24637600</v>
+        <v>23707310</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24637600</v>
+        <v>23707310</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24637600</v>
+        <v>23707310</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24637600</v>
+        <v>23707310</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24637600</v>
+        <v>23707310</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
